--- a/Table_EV3.xlsx
+++ b/Table_EV3.xlsx
@@ -20,7 +20,10 @@
     <sheet name="DMA_OSRC2_vs_HK2" sheetId="11" r:id="rId11"/>
     <sheet name="DMA_RFX631_vs_HK2" sheetId="12" r:id="rId12"/>
     <sheet name="DMA_FeatureMetadata" sheetId="13" r:id="rId13"/>
-    <sheet name="MetalinksDB_metabolite_links" sheetId="14" r:id="rId14"/>
+    <sheet name="Rules_MCA2Cond" sheetId="14" r:id="rId14"/>
+    <sheet name="MCA2Cond_786M1A_vs_HK2" sheetId="15" r:id="rId15"/>
+    <sheet name="MCA2Cond_Summary" sheetId="16" r:id="rId16"/>
+    <sheet name="MetalinksDB_metabolite_links" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -364,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -530,6 +533,42 @@
         </is>
       </c>
       <c r="B14" t="inlineStr">
+        <is>
+          <t>MCA2Cond Clustering rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sheet 14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCA2Cond biological regulated clustering 786M1A versus HK2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sheet 15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Summary of MCA2Cond biological regulated clustering.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sheet 16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>MetalinksDB metabolite-transporter, -receptor and -enzyme links to the measured metabolites.</t>
         </is>
@@ -26039,6 +26078,5575 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G109"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Intra</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>CoRe</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Core_Direction</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RG1_All</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>R2_Significant</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>RG3_Change</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RG3_ChangeNum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Opposite (Released UP)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Opposite (Released UP)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Opposite (Released UP)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Opposite (Released DOWN)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Opposite (Released DOWN)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Opposite (Released UP)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Both_UP (Released)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Both_UP (Released)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Both_UP (Released)</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G24">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Opposite (Released UP)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="G25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Opposite (Released DOWN)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G27">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Both_UP (Released)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="G31">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe DOWN_Released</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released)</t>
+        </is>
+      </c>
+      <c r="G32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Not Significant_Released</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Significant Negative_Released</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Significant Positive_Released</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe UP_Released</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released)</t>
+        </is>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Intra DOWN+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed UP)</t>
+        </is>
+      </c>
+      <c r="G43">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="G44">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Both_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G48">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Intra UP+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Both_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Both_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="G49">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="G50">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G51">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G52">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Intra Not Detected+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="G56">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G57">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G58">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G60">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="G61">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Opposite (Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="G62">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G63">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G66">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Both_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="G67">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe DOWN_Consumed</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Consumed)</t>
+        </is>
+      </c>
+      <c r="G68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G69">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Not Significant_Consumed</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Significant Negative_Consumed</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe Significant Positive_Consumed</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Consumed</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Intra Not Significant+ CoRe UP_Consumed</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Consumed)</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Intra DOWN + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed UP)</t>
+        </is>
+      </c>
+      <c r="G79">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="G80">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Both_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Intra UP + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Both_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Both_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G85">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G86">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G87">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Intra Not Detected + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G91">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Both_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G92">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G93">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G94">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G95">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G96">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Intra Significant Negative + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed UP)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G97">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Opposite (Released/Consumed DOWN)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G98">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G99">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G101">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Intra Significant Positive + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Both_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G103">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DOWN</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe DOWN_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>CoRe_DOWN (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G104">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Not Detected</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe Not Detected</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G105">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe Not Significant_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G106">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Significant Negative</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe Significant Negative_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G107">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Significant Positive</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe Significant Positive_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G108">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Not Significant</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Released/Consumed</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Intra Not Significant + CoRe UP_Released/Consumed</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>CoRe_UP (Released/Consumed)</t>
+        </is>
+      </c>
+      <c r="G109">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A200"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metabolite.Intra_DF_Detected.Intra_DF_ValueCol.Intra_DF_PadjCol.Intra_DF_Cutoff.Intra_DF_Cutoff_Specific.x.core_DF_Detected.core_DF_ValueCol.core_DF_PadjCol.core_DF_Cutoff.core_DF_Cutoff_Specific.BG_method.RG1_All.RG2_Significant.RG3_Change.Cond1_DF_.Log2FC.Cond1_DF_.p.adj.Intra_DF_t.val.Intra_DF_HMDB.Intra_DF_KEGG.ID.Intra_DF_KEGGCompound.Intra_DF_Pathway.Intra_DF_786.M1A_1.Intra_DF_786.M1A_2.Intra_DF_786.M1A_3.Intra_DF_HK2_1.Intra_DF_HK2_2.Intra_DF_HK2_3.Intra_DF_Cutoff_Specific.y.Cond2_DF_.Log2.Distance..Cond2_DF_.p.adj.core_DF_t.val.core_DF_Mean_786.M1A.core_DF_core_786.M1A.core_DF_Mean_HK2.core_DF_core_HK2.core_DF_core_specific.core_DF_core_Direction.core_DF_MS51.16.core_DF_MS51.17.core_DF_MS51.18.core_DF_MS51.19.core_DF_MS51.20.core_DF_MS51.07.core_DF_MS51.08.core_DF_MS51.09.core_DF_MS51.10.core_DF_HMDB.core_DF_KEGG.ID.core_DF_KEGGCompound.core_DF_Pathway</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2-aminoadipic acid,TRUE,0.152981575,0.237848335,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.152981575,0.237848335,-756331.8573,HMDB0302754,NA,NA,Not assigned,7515754.961,7794628.795,7241957.187,5801815.747,7322390.03,7159139.595,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2-hydroxyglutarate,TRUE,0.931522626,6.45258554667905e-5,UP,UP,TRUE,31.5259431109401,0.3447870348807577,No Change,Not Significant,TRUE,Intra UP + core Not Significant_Released/Consumed,None,None,0.931522626,6.45258554667905e-5,-202115036.9,HMDB0059655,C02630,2-Hydroxyglutarate,Citrate cycle (TCA cycle),424350094.4,432815728.4,417484370.5,188417805,228825446.1,251061831.5,UP,31.5259431109401,0.3447870348807577,-3092107028.8653574,3092107028.86536,Released,-4.41446900367737e-07,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,5445671696.947043,3041583921.4769626,2364979959.6335263,600387749.6408762,4007911816.6283746,-868601575.3942189,1108346024.8484714,-189633550.0132567,-50110899.44099755,HMDB0059655,C02630,2-Hydroxyglutarate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2-ketoglutarate,TRUE,1.351253503,7.00253626539915e-6,UP,UP,TRUE,34.39775158413,1.0997508459453798e-9,UP,UP,TRUE,Intra UP + core UP_Released/Consumed,Both_UP (Released/Consumed),Both_UP (Released/Consumed),1.351253503,7.00253626539915e-6,-596239369.8,HMDB0000208,C00026,2-Oxoglutarate,Citrate cycle (TCA cycle),959154967.8,979152170.6,1003428045,326367919.1,366703618.4,459945536.8,UP,34.39775158413,1.0997508459453798e-9,-22633671597.776337,22633671597.7763,Released,-8.94069671630859e-07,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,28056643231.16079,22341957662.640594,19876068811.33025,22338213828.190865,20555474455.55909,1530912430.0615942,3684365990.4454947,-9097094734.637407,3881816314.130315,HMDB0000208,C00026,2-Oxoglutarate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2/3-phosphoglycerate,TRUE,0.699344846,9.46101e-4,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.699344846,9.46101e-4,-19337537.43,HMDB0060180,C00197,3-Phospho-D-glycerate,Glycolysis / Gluconeogenesis,56869709.98,48343621.46,45802901.95,30931592.11,32564866.75,29507162.25,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3-Dehydro-L-threonate,FALSE,NA,NA,No Change,Not Detected,TRUE,-30.2476462244456,0.9999999304750602,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-30.2476462244456,0.9999999304750602,1274819834.183158,-1274819834.18323,Consumed,-7.35372304916382e-06,Consumed,Consumed,Consumed,9905712215.07218,-1871784882.8935628,-12106631836.460861,-15996801077.152159,13695406410.518244,28673393701.28635,39313101752.01325,-67782920598.13456,-203574855.1650723,NA,NA,NA,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4-guanidinobutanoate,TRUE,-1.154155178,1.70987e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.154155178,1.70987e-4,2371361.737,HMDB0003464,C01035,4-Guanidinobutanoate,Arginine and proline metabolism,1919684.721,1885078.616,2000096.131,4418820.279,4133882.632,4366241.768,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4-hydroxyphenyllactate,TRUE,-0.916170233,6.16612213510948e-8,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.916170233,6.16612213510948e-8,1905690.971,HMDB0000755,C03672,3-(4-Hydroxyphenyl)lactate,Not assigned,2200691.109,2038710.18,2205281.755,3963104.396,3971958.327,4226693.233,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>5-aminolevulinic acid,TRUE,-0.177727149,0.491516504,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.177727149,0.491516504,525130.264,HMDB0001149,C00430,5-Aminolevulinate,Not assigned,3774612.516,3938304.363,4303746.118,4028434.891,4373206.793,5190412.105,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>5-aminovaleric acid*,TRUE,0.629750657,0.010083571,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.629750657,0.010083571,-22623638.87,NA,NA,NA,Not assigned,69248646.6,66983507.08,55649763.56,39898613.12,43445126.01,40667261.49,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5-methylthioadenosine (MTA),TRUE,-0.502754794,0.076387425,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.502754794,0.076387425,7369026.23,HMDB0001173,C00170,5'-Methylthioadenosine,Cysteine and methionine metabolism,13467706.79,19486387.95,20071093.72,24864886.37,22428867.43,27838513.35,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6-phosphogluconate,TRUE,-0.250771648,0.930351089,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.250771648,0.930351089,197774.2409,HMDB0001316,C00345,6-Phospho-D-gluconate,Pentose phosphate pathway,972022.2739,707684.3146,1445621.317,1061037.696,1255715.294,1401897.638,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acetyl-CoA,TRUE,-0.008968514,0.999931165,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.008968514,0.999931165,16711.52338,HMDB0001206,C00024,Acetyl-CoA,Citrate cycle (TCA cycle),2924310.275,2186800.613,2928606.145,2894328.771,2296943.7,2898579.132,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acetylcarnitine,TRUE,0.065328888,0.995147797,No Change,Not Significant,TRUE,-38.3870522710167,0.06537357238140207,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released/Consumed,None,None,0.065328888,0.995147797,-194906873.3,HMDB0000201,C02571,O-Acetylcarnitine,Fatty acyl carnitines,4022430586,3567130318,5617724322,5947039758,3143517363,3532007486,Not Significant,-38.3870522710167,0.06537357238140207,359462986906.5166,-359462986906.515,Consumed,0.000949859619140625,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-356638276040.5191,-379917701289.25,-297445077870.59174,-325213646459.2178,-438100232872.9975,-67547592847.63014,-234677799644.69583,218513442831.441,83711949660.88876,HMDB0000201,C02571,O-Acetylcarnitine,Fatty acyl carnitines</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acetylcholine,TRUE,-0.45939283,0.005848579,No Change,Significant Negative,TRUE,-30.0867461826883,4.99615552002175e-4,DOWN,DOWN,TRUE,Intra Significant Negative + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.45939283,0.005848579,10639302.78,HMDB0000895,C01996,Acetylcholine,Glycerophospholipid metabolism,28297226.09,28306527.94,28519059.86,43890849.74,36981810.98,36168061.53,Significant Negative,-30.0867461826883,4.99615552002175e-4,1140284111.3136091,-1140284111.31361,Consumed,9.20146703720093e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-929117918.2542715,-1217951806.7605405,-907725947.7786033,-1216114751.1676984,-1430510132.6069257,-496576017.1817,-124297108.54948749,526295912.9105642,94577212.82062697,HMDB0000895,C01996,Acetylcholine,Glycerophospholipid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acetylornithine,FALSE,NA,NA,No Change,Not Detected,TRUE,32.652736846585,0.001279264927067203,UP,UP,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,32.652736846585,0.001279264927067203,-6752323351.138543,6752323351.13854,Released,-4.4703483581543e-08,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,7418575312.429144,4720343099.011327,6181534901.044759,9501247793.841635,5939915649.365829,2551741127.6261606,-630043502.2454171,-456525416.075906,-1465172209.3048377,HMDB0003357,C00437,N-Acetylornithine,Arginine and proline metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>aconitate,TRUE,0.903226327,0.010961578,UP,UP,TRUE,-32.581449057611,3.268940673706311e-12,DOWN,DOWN,TRUE,Intra UP + core DOWN_Consumed,Opposite (Consumed DOWN),Opposite (Consumed DOWN),0.903226327,0.010961578,-46075390.99,HMDB0000072,C00417,cis-Aconitate,Citrate cycle (TCA cycle),87829576.53,93936705.65,115296043.9,66710215.18,42899324.16,49226613.75,UP,-32.581449057611,3.268940673706311e-12,6426780518.516189,-6426780518.51619,Consumed,-9.31322574615479e-07,Consumed,Consumed,Consumed,-5865088200.321102,-6431671419.581658,-6503096253.665237,-6848155621.3107395,-6485891097.702192,1186119567.8546586,-610503913.8039101,-406215498.01261455,-169400156.03813764,HMDB0000072,C00417,cis-Aconitate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adenosine,TRUE,-0.206429865,0.963801863,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.206429865,0.963801863,1683164.989,HMDB0000050,C00212,Adenosine,Purine metabolism,11604889.52,10714045.01,10506368.47,13885363.06,11239887.71,12749547.19,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADP,TRUE,-0.175607423,0.751148925,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.175607423,0.751148925,5802994.946,HMDB0001341,C00008,ADP,Purine metabolism,49965436.96,35328279.23,49201082.5,56618979.32,45298596.35,49986207.86,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADP-ribose,TRUE,0.171096596,0.213558637,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.171096596,0.213558637,-209763.1931,HMDB0001178,C00301,ADP-ribose,Purine metabolism,1657369.439,2019794.938,1949899.335,1682394.658,1676294.212,1639085.261,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>alanine,TRUE,-1.718677942,1.85934424336009e-5,DOWN,DOWN,TRUE,-36.0704911984442,4.564570943443869e-12,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-1.718677942,1.85934424336009e-5,601764151,HMDB0000161,C00041,L-Alanine,Amino acid metabolism,262139689.1,267364892.6,258369450.2,1000105967,857373599.8,735686918.2,DOWN,-36.0704911984442,4.564570943443869e-12,72160545741.87466,-72160545741.8747,Consumed,1.19209289550781e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-86911310253.07578,-72941035266.88689,-65809784272.28617,-69635534717.79749,-65505064199.32706,-6454143744.995457,1426053214.933169,-5215874227.534016,10243964757.596304,HMDB0000161,C00041,L-Alanine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AMP,TRUE,0.155948417,0.297992745,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.155948417,0.297992745,-1585840.778,HMDB0000045,C00020,AMP,Purine metabolism,16555562.09,14352308.33,15526072.16,13918047.79,13253745.27,14504627.19,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>arginine,TRUE,0.389145076,0.120831737,No Change,Not Significant,TRUE,36.6319692759177,0.9411031154931908,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released,None,None,0.389145076,0.120831737,-31336310.8,HMDB0000517,C00062,L-Arginine,Amino acid metabolism,135157876,126922947.4,135557750.8,89109569.06,87373746.53,127146326.2,Not Significant,36.6319692759177,0.9411031154931908,-106493120307.8371,106493120307.837,Released,5.7220458984375e-05,Released,Released,Released,216146922500.63803,123584771692.03416,-184582255060.27814,137947177033.69067,239368985373.09988,124885985747.9214,174141953767.7149,-154239029795.80392,-144788909719.83215,HMDB0000517,C00062,L-Arginine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>argininosuccinate,TRUE,-0.239569127,0.109280255,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.239569127,0.109280255,84953.79725,HMDB0000052,C03406,N-(L-Arginino)succinate,Alanine, aspartate and glutamate metabolism,454662.3374,444031.6702,512186.148,617283.959,553005.4654,495452.123,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>asparagine,TRUE,-1.755313391,3.23967641602252e-9,DOWN,DOWN,TRUE,31.7054265305565,0.004821138745304099,UP,UP,TRUE,Intra DOWN + core UP_Released,Opposite (Released UP),Opposite (Released UP),-1.755313391,3.23967641602252e-9,69701487.09,HMDB0000168,C00152,L-Asparagine,Amino acid metabolism,30095626.63,29573451.26,28337981.36,100771574.1,101548392.2,94791554.21,DOWN,31.7054265305565,0.004821138745304099,-3501744143.756177,3501744143.75618,Released,3.66568565368652e-06,Released,Released,Released,3427679273.0652313,2677073884.1455255,4884996692.4928875,3124738477.662143,3394232391.41509,2212116481.547353,1022104506.3487697,-4269578942.005922,1035357954.109814,HMDB0000168,C00152,L-Asparagine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>aspartate,TRUE,0.520609932,3.34962e-4,No Change,Significant Positive,TRUE,-34.3542231614157,1.0487721802121541e-11,DOWN,DOWN,TRUE,Intra Significant Positive + core DOWN_Consumed,Opposite (Consumed DOWN),core_DOWN (Consumed),0.520609932,3.34962e-4,-466200707,HMDB0000191,C00049,L-Aspartate,Amino acid metabolism,1586907437,1591156371,1438959084,964215886.9,1173661258,1080543625,Significant Positive,-34.3542231614157,1.0487721802121541e-11,21960976606.515976,-21960976606.516,Consumed,-1.72853469848633e-06,Consumed,Consumed,Consumed,-20078854995.00557,-23024873123.533096,-23695204780.011406,-22469858974.092056,-20536091159.937737,1216173971.112008,2386511959.5319633,-2796694642.6828322,-805991287.9611461,HMDB0000191,C00049,L-Aspartate,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ATP,TRUE,-0.328118665,0.73820125,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.328118665,0.73820125,44822513.07,HMDB0000538,C00002,ATP,Purine metabolism,199949598.3,119442957.9,207156285.7,280356916.6,172910971.9,207748492.5,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>beta-alanine,TRUE,-1.24766475,9.49012645923286e-6,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.24766475,9.49012645923286e-6,62061788.17,HMDB0000056,C00099,beta-Alanine,Pyrimidine metabolism,46555224.94,46974652.96,41920267.96,117847309.7,108571737.9,95216462.73,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>beta-citrylglutamic acid,TRUE,-0.270084766,0.017765048,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.270084766,0.017765048,38555657.61,HMDB0013220,NA,NA,Not assigned,199709003.2,186168366.8,175943671.1,223143700.3,226366148,227978165.8,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>betaine,TRUE,-0.960129224,1.75120052434696e-5,DOWN,DOWN,TRUE,39.0936024442182,0.0017858012364712073,UP,UP,TRUE,Intra DOWN + core UP_Released,Opposite (Released UP),Opposite (Released UP),-0.960129224,1.75120052434696e-5,3333163634,HMDB0000043,C00719,Betaine,Not assigned,3624687372,3165614079,3785752029,7194708605,6606221432,6774614343,DOWN,39.0936024442182,0.0017858012364712073,-586606639558.5292,586606639558.529,Released,1.9073486328125e-06,Released,Released,Released,688358341457.485,490864850765.0183,657311755851.1819,724283773820.603,372214475898.35626,222640096431.77213,-24221141664.355583,-466988404785.12866,268569450017.71213,HMDB0000043,C00719,Betaine,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>butyryl-carnitine,FALSE,NA,NA,No Change,Not Detected,TRUE,-32.8566106389332,1.7020276299462012e-9,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-32.8566106389332,1.7020276299462012e-9,7777237439.114677,-7777237439.11468,Consumed,4.4703483581543e-08,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-7234381016.309397,-6049981016.574119,-7966843561.733514,-7224121792.136499,-10410859808.819847,-1725651088.8349278,-378940309.1250474,1602911966.7021985,501679431.25777686,HMDB0002013,C02862,O-Butanoylcarnitine,Fatty acyl carnitines</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>butyrylcarnitine C4,TRUE,-0.343202774,0.024085846,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.343202774,0.024085846,177963178.7,HMDB0002013,C02862,NA,Fatty acyl carnitines,603212737.5,663736011.7,720950711,855908527.7,919639157.1,746241311.4,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cAMP,TRUE,-0.366046161,0.014884301,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.366046161,0.014884301,96883.09658,HMDB0000058,C00575,Cyclic AMP,Purine metabolism,277505.2482,342739.3559,386103.4624,439278.7244,424593.8691,433124.7626,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>carbamoyl phosphate,FALSE,NA,NA,No Change,Not Detected,TRUE,29.6346116851836,0.5228459408374393,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,29.6346116851836,0.5228459408374393,-833502730.8994387,833502730.89944,Released,9.23871994018555e-07,Released,Released,Released,544741981.3927903,632898115.04515,1989818101.1082458,816820278.9497858,183235178.0012275,200618838.98947328,-354809141.0600828,549923002.2001165,-395732700.1295033,HMDB0001096,C00169,Carbamoyl phosphate,Purine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>carnitinamide,TRUE,0.423390844,2.5252e-4,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.423390844,2.5252e-4,-901949.4253,NA,C02290,L-Carnitinamide,Not assigned,3340599.955,3525496.228,3773026.241,2741568.915,2471171.548,2720533.686,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>carnitine,TRUE,0.497744753,0.012689164,No Change,Significant Positive,TRUE,-34.9414466873087,0.989816161153938,No Change,Not Significant,TRUE,Intra Significant Positive + core Not Significant_Consumed,None,None,0.497744753,0.012689164,-4957387471,NA,C00487,Carnitine,Fatty acyl carnitines,17243583705,17526479429,16199180850,14164377441,11991811961,9940892170,Significant Positive,-34.9414466873087,0.989816161153938,32993132014.94961,-32993132014.9497,Consumed,-0.000118255615234375,Consumed,Consumed,Consumed,14730581499.466398,-9364392436.864042,-72221357329.17183,-81344211251.13815,-16766280557.040747,-78986754836.66919,36801597623.693436,-9829425338.399849,52014582551.37513,NA,C00487,Carnitine,Fatty acyl carnitines</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>carnosine,TRUE,0.23799561,0.76377695,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.23799561,0.76377695,-1552428.723,HMDB0000033,C00386,Carnosine,Not assigned,11785035.5,8647827.492,10191572.18,7123793.577,7167033.277,11676322.15,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CDP,TRUE,0.035559133,0.999764909,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.035559133,0.999764909,-117577.0874,HMDB0001546,C00112,CDP,Pyrimidine metabolism,5739549.015,3241414.792,5507038.987,6911889.622,3342933.182,3880448.728,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CDP-ethanolamine,TRUE,-2.502508444,2.17313e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-2.502508444,2.17313e-4,6245461.808,HMDB0001564,C00570,CDP-ethanolamine,Glycerophospholipid metabolism,1086177.404,1561509.215,1367225.732,9615337.945,7007144.061,6128815.77,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>choline,TRUE,-0.176043993,0.603034308,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.176043993,0.603034308,70553502.45,HMDB0000097,C00114,Choline,Glycerophospholipid metabolism,594830278.1,493153219.3,542913336.5,702639155,565866917.3,574051269,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>citicoline,TRUE,-1.845044776,2.2967159618581e-8,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.845044776,2.2967159618581e-8,14974890.8,HMDB0001413,C00307,CDP-choline,Glycerophospholipid metabolism,5444321.872,5723543.661,6159898.903,19924586.54,20523734.33,21804115.95,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>citrate,TRUE,0.588218678,0.002706419,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.588218678,0.002706419,-715371351,HMDB0000094,C00158,Citrate,Citrate cycle (TCA cycle),2010790503,1980188252,2418463675,1598687203,1234621473,1430019701,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>citrulline,TRUE,-0.503041308,2.40632617538594e-5,No Change,Significant Negative,TRUE,-36.1994129786645,1.1407476668834349e-6,DOWN,DOWN,TRUE,Intra Significant Negative + core DOWN_Consumed,Both_DOWN (Consumed),core_DOWN (Consumed),-0.503041308,2.40632617538594e-5,113695879.5,HMDB0000904,C00327,L-Citrulline,Arginine and proline metabolism,275324809.3,278046331.6,264196679.6,384972174.9,381069604,392613680.2,Significant Negative,-36.1994129786645,1.1407476668834349e-6,78905837181.74702,-78905837181.7471,Consumed,-5.91278076171875e-05,Consumed,Consumed,Consumed,-71944710436.11852,-49444293823.91433,-97270509029.95593,-99980190973.05305,-75889481645.69342,-20311592865.700745,19615311684.57498,9449456330.717314,-8753175149.591787,HMDB0000904,C00327,L-Citrulline,Arginine and proline metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CMP,TRUE,0.31724884800000003,0.939097,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.31724884800000003,0.939097,-200746.8065,HMDB0000095,C00055,CMP,Pyrimidine metabolism,1280443.657,690823.8148,1079579.437,1338784.622,529560.8126,580261.0539,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CMP-2-aminoethylphosphonate,TRUE,-0.936924484,0.009145457,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.936924484,0.009145457,1316653.662,HMDB0060067,C05673,CMP-2-aminoethylphosphonate,Not assigned,1242478.807,1739740.979,1337308.343,2890089.045,3027421.652,2351978.417,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CMP-acetylneuraminic acid,TRUE,0.029015568,0.967674622,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.029015568,0.967674622,-134528.3668,HMDB0001176,C00128,CMP-N-acetylneuraminate,Not assigned,6614308.173,6972180.206,6682802.025,6634164.874,6843428.704,6388111.726,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>creatine,TRUE,0.563141932,2.83448345389514e-5,No Change,Significant Positive,TRUE,38.8756426943078,1.3946195843272946e-4,UP,UP,TRUE,Intra Significant Positive + core UP_Released/Consumed,Both_UP (Released/Consumed),core_UP (Released/Consumed),0.563141932,2.83448345389514e-5,-16753312404,HMDB0000064,C00300,Creatine,Arginine and proline metabolism,52612707204,51257739520,51649560335,31507318577,35929464750,37823286520,Significant Positive,38.8756426943078,1.3946195843272946e-4,-504352934098.96234,504352934098.962,NA,0,NA,No Change,Released/Consumed,327377007138.8107,374394663895.9156,664021568772.1547,559157912452.1274,596813518235.8033,-12057751702.178347,83562457461.1413,-86756331746.53214,15251625987.569185,HMDB0000064,C00300,Creatine,Arginine and proline metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>creatinine,TRUE,0.199103129,0.264407668,No Change,Not Significant,TRUE,36.7513372392316,0.6157485755118839,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released,None,None,0.199103129,0.264407668,-237001434.5,HMDB0000562,C00791,Creatinine,Arginine and proline metabolism,1955600557,1774650243,1785340689,1499168576,1492781436,1812637173,Not Significant,36.7513372392316,0.6157485755118839,-115679096985.11432,115679096985.114,Released,0.00023651123046875,Released,Released,Released,7024739250.436813,36751201103.28212,292650795396.19183,108314205604.71599,133654543570.94539,35993185510.8919,-29584087145.775063,-76854565797.80908,70445467432.69319,HMDB0000562,C00791,Creatinine,Arginine and proline metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>CTP,TRUE,-0.063991405,0.999011178,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.063991405,0.999011178,500180.0391,HMDB0000082,C00063,CTP,Pyrimidine metabolism,12994987.87,6780227.332,13309944.87,17275778.75,7801125.01,9508796.434,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cyclic ADP-ribose,TRUE,0.083210659,0.25522569,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.083210659,0.25522569,-1051822.248,HMDB0249529,C13050,Cyclic ADP-ribose,Purine metabolism,17862090.9,18924578.26,19515281.17,18307142.35,17492036.1,17347305.14,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cystathionine,TRUE,-3.751559454,2.12008199540481e-6,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-3.751559454,2.12008199540481e-6,6062586.349,HMDB0000099,C02291,L-Cystathionine,Cysteine and methionine metabolism,337234.5447,572911.8656,548504.168,7512091.249,6612123.546,5522194.831,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cysteic acid,TRUE,1.718272103,0.001399381,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.718272103,0.001399381,-271727.4685,HMDB0002757,C00506,L-Cysteate,Cysteine and methionine metabolism,311339.9929,404028.5999,455723.2597,109495.3907,105348.6684,141065.3879,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cysteinylglycine,TRUE,-0.826373053,8.4271e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.826373053,8.4271e-4,9505050.613,HMDB0000078,C01419,Cys-Gly,Glutathione metabolism,12995733.51,13020566.89,10862056.68,23351149.88,21940313.78,20102045.25,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cystine,FALSE,NA,NA,No Change,Not Detected,TRUE,-32.9771004008206,0.09439473988280367,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-32.9771004008206,0.09439473988280367,8454664736.931053,-8454664736.93104,Consumed,5.48362731933594e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-4452603146.433538,-10076574885.401619,-11577234132.93185,-8884216028.50108,-7282695491.387117,-4573819744.794884,-4861293426.745634,15570158349.379692,-6135045177.839152,HMDB0000192,C00491,L-Cystine,Cysteine and methionine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cytidine,TRUE,-0.186967187,0.842141706,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.186967187,0.842141706,409402.4828,HMDB0000089,C00475,Cytidine,Pyrimidine metabolism,2999977.355,2393359.775,3483037.648,3392418.881,2830448.362,3881714.985,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cytosine,TRUE,0.140228896,0.668656467,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.140228896,0.668656467,-332910.8662,HMDB0000630,C00380,Cytosine,Pyrimidine metabolism,3682260.137,3318310.492,3781988.593,3030263.337,3003927.099,3749636.187,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>dATP,TRUE,-1.011501581,0.372031975,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.011501581,0.372031975,189177.5774,HMDB0001532,C00131,dATP,Purine metabolism,205533.9659,85288.81726,267767.8604,558551.6235,233062.8026,334508.9498,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>dCTP,TRUE,-0.23256268,0.984328184,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.23256268,0.984328184,52747.48119,HMDB0000998,C00458,dCTP,Pyrimidine metabolism,420233.9147,89075.77443,395345.7595,620847.1355,183590.29,258460.4667,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>deoxyadenosine,TRUE,-0.215236488,0.943280846,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.215236488,0.943280846,71734.70489,HMDB0000101,C00559,Deoxyadenosine,Purine metabolism,445061.7899,371461.0344,521027.7104,480532.1813,387237.5535,684984.9146,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>deoxycytidine,TRUE,-0.119221594,0.909263496,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.119221594,0.909263496,401462.3678,HMDB0000014,C00881,Deoxycytidine,Pyrimidine metabolism,4553336.893,4740239.826,4686755.9,5920548.102,4417177.642,4846993.979,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>deoxyribose 5-phosphate,TRUE,1.765968047,5.51612047311467e-5,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.765968047,5.51612047311467e-5,-1601057.022,HMDB0001031,C00673,2-Deoxy-D-ribose 5-phosphate,Pentose phosphate pathway,2244233.598,2513221.274,2046186.178,761603.1527,745670.8854,493195.9455,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>dihydroorotate,TRUE,-0.452560317,0.970371375,No Change,Not Significant,TRUE,26.683041363669,9.250175709585307e-5,No Change,Significant Positive,TRUE,Intra Not Significant + core Significant Positive_Released,None,None,-0.452560317,0.970371375,7249404.735,HMDB0003349,C00337,(S)-Dihydroorotate,Pyrimidine metabolism,17728016.83,20614559.83,20680979.19,19478639.73,47944721.15,13348409.18,Not Significant,26.683041363669,9.250175709585307e-5,-107744677.60938781,107744677.609388,Released,1.49011611938477e-08,Released,Released,Released,126351533.91844109,65602995.35960465,147647811.63646784,70211148.99279445,128909898.13963166,-21080482.9972008,-18986954.415806595,-19578826.467237778,59646263.88024523,HMDB0003349,C00337,(S)-Dihydroorotate,Pyrimidine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>dihydroxyacetone phosphate,TRUE,0.381262942,0.200991927,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.381262942,0.200991927,-10971445.32,HMDB0001473,C00111,Glycerone phosphate,Glycolysis / Gluconeogenesis,38715576.38,53310496.29,49702620.4,35784384.42,37493731.6,35536241.09,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>dimethylarginine (ADMA+SDMA),TRUE,0.088095271,0.808249098,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.088095271,0.808249098,-466522.4291,NA,NA,NA,Not assigned,7795771.752,7591008.8,8240183.064,7913502.801,6472579.795,7841313.732,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>dTTP,TRUE,-0.343592993,0.565655198,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.343592993,0.565655198,745878.2771,HMDB0001342,C00459,dTTP,Pyrimidine metabolism,3125601.009,2031230.851,3164208.913,4487385.139,3003722.799,3067567.667,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FAD,TRUE,0.421124009,0.749377892,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.421124009,0.749377892,-182586.7694,HMDB0001248,C00016,FAD,Vitamin digestion and absorption,625232.3311,536471.2602,1002010.197,618750.6275,379446.5154,617756.3369,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>fructose,TRUE,0.794222703,0.005979162,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.794222703,0.005979162,-4082016.213,HMDB0000660,C02336,beta-D-Fructose,Not assigned,10370792.74,9466659.49,9089341.159,5105695.149,4912476.497,6662573.109,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>fructose 1,6-bisphosphate,TRUE,0.116017425,0.649118769,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.116017425,0.649118769,-1323149.597,HMDB0001058,C00354,D-Fructose 1,6-bisphosphate,Glycolysis / Gluconeogenesis,18142483.61,15751090.65,17478472.2,14727001.3,16309296.75,16366299.62,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fructose 6-Phosphate,TRUE,0.047633455,0.99219552,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.047633455,0.99219552,-157002.3864,HMDB0000124,C00085,D-Fructose 6-phosphate,Not assigned,4504988.376,4596929.191,5400479.304,4422697.632,4913412.279,4695279.801,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>fumarate,TRUE,0.053063816,0.943849051,No Change,Not Significant,TRUE,23.4922797898379,1,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released,None,None,0.053063816,0.943849051,-4241662.336,HMDB0000134,C00122,Fumarate,Citrate cycle (TCA cycle),117455414.5,123939283.6,110972786.8,106582182,114559051,118501264.9,Not Significant,23.4922797898379,1,-11799969.459468126,11799969.4594641,Released,3.72529029846191e-08,Released,Released,Released,901191477.834818,-217509595.97295648,-779926743.8811789,-940872643.1687946,1096117352.4854324,1998071059.4265454,2984291976.737173,-5054780755.7889595,72417719.62524119,HMDB0000134,C00122,Fumarate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>GDP,TRUE,0.071032132,0.998282965,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.071032132,0.998282965,-262885.617,HMDB0001201,C00035,GDP,Purine metabolism,6342337.303,3620835.184,6452372.474,7083787.41,4029030.293,4514070.407,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GDP-hexose,TRUE,0.409592971,0.104183848,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.409592971,0.104183848,-308657.7374,NA,NA,NA,Purine metabolism,1367487.765,987289.489,1391610.757,867391.972,900009.8892,1053012.938,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>gluconate,TRUE,-2.779471575,5.7542779763331e-8,DOWN,DOWN,TRUE,-33.2222625587053,0.9764802836256037,No Change,Not Significant,TRUE,Intra DOWN + core Not Significant_Released/Consumed,None,None,-2.779471575,5.7542779763331e-8,2406754289,HMDB0000625,C00257,D-Gluconic acid,Pentose phosphate pathway,374261790.4,420595122,436007868.6,2985441446,2931277222,2534408980,DOWN,-33.2222625587053,0.9764802836256037,10020688315.333073,-10020688315.3331,Consumed,3.75509262084961e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-10695251046.578869,-23232263083.501053,-18911380943.764263,-29309653342.030617,32045106839.209457,589183499.520678,1766463381.9211853,-4584014632.709254,2228367751.267406,HMDB0000625,C00257,D-Gluconic acid,Pentose phosphate pathway</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>glucose,TRUE,0.568506661,0.519064647,No Change,Not Significant,TRUE,-35.3284749073644,2.5923707624997405e-13,DOWN,DOWN,TRUE,Intra Not Significant + core DOWN_Released/Consumed,core_DOWN (Released/Consumed),core_DOWN (Released/Consumed),0.568506661,0.519064647,-15133821.3,HMDB0003345,C00267,alpha-D-Glucose,Glycolysis / Gluconeogenesis,55565990.19,38150612.16,45686139.61,18410559.68,22268182.16,53322536.22,Not Significant,-35.3284749073644,2.5923707624997405e-13,43145017370.85918,-43145017370.8592,Consumed,2.08616256713867e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-44694436005.35603,-41843616909.43194,-42129491840.45848,-43663206426.46812,-43394335672.58125,-5028619624.652876,734035324.654786,7872466998.972409,-3577882698.9743185,HMDB0003345,C00267,alpha-D-Glucose,Glycolysis / Gluconeogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>glucose 1-phosphate,TRUE,-0.64528621,0.001172849,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.64528621,0.001172849,757090.3286,HMDB0001586,C00103,D-Glucose 1-phosphate,Glycolysis / Gluconeogenesis,1185105.868,1438821.861,1402794.786,2066096.576,2108934.699,2122962.227,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>glucose 6-phosphate,TRUE,-0.084052557,0.995274762,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.084052557,0.995274762,514974.3388,HMDB0001401,C00092,D-Glucose 6-phosphate,Glycolysis / Gluconeogenesis,7968053.521,7076673.944,10707681.42,7478831.978,9361106.455,10457393.46,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>glucuronic acid,TRUE,0.335183405,0.110201477,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.335183405,0.110201477,-2012508.192,HMDB0000127,C00191,D-Glucuronate,Not assigned,10041706.3,9410405.651,9670126.134,9162723.898,7820849.141,6101140.476,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>glutamate,TRUE,0.424847059,1.7292e-4,No Change,Significant Positive,TRUE,32.1776914377899,0.9967493574227422,No Change,Not Significant,TRUE,Intra Significant Positive + core Not Significant_Released/Consumed,None,None,0.424847059,1.7292e-4,-2571171216,HMDB0000148,C00025,L-Glutamate,Amino acid metabolism,9854317531,10639801927,9745193666,6963813664,7962084413,7599901398,Significant Positive,32.1776914377899,0.9967493574227422,-4857919501.205195,4857919501.20515,Released,-1.45435333251953e-05,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,4545383626.405889,-227919854.9347031,1395949094.1012948,14216122212.017042,4360062428.436229,15413910962.16045,15015065646.624634,-21840968399.830997,-8588008208.9541445,HMDB0000148,C00025,L-Glutamate,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>glutamine,TRUE,-0.167274781,0.855495652,No Change,Not Significant,TRUE,38.0072009499906,2.9976021664879227e-14,UP,UP,TRUE,Intra Not Significant + core UP_Released/Consumed,core_UP (Released/Consumed),core_UP (Released/Consumed),-0.167274781,0.855495652,152921386.5,HMDB0000641,C00064,L-Glutamine,Amino acid metabolism,1396287221,1186213863,1149252388,998301998.5,1424528207,1767687426,Not Significant,38.0072009499906,2.9976021664879227e-14,-276253339795.0781,276253339795.078,Released,-1.44243240356445e-05,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,273934030917.3308,281627252517.2309,277813965717.64813,280545730532.2492,267345719290.932,20105641591.19911,2520386231.02276,-16661398877.70642,-5964628944.515505,HMDB0000641,C00064,L-Glutamine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>glutamylcysteine,TRUE,-0.960697276,0.003043014,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.960697276,0.003043014,460734.4474,HMDB0001049,C00669,gamma-L-Glutamyl-L-cysteine,Glutathione metabolism,604764.3624,433096.9101,422855.1084,925851.7591,983351.3363,933716.6278,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>glutamylglutamate,TRUE,0.369219269,0.118410597,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.369219269,0.118410597,-752643.7062,HMDB0028818,C01425,Glutamyl-glutamic acid,Amino acid metabolism,3477770.696,3562135.696,2959848.406,2338642.737,2763773.032,2639407.912,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>glutamyllysine,TRUE,-0.060062828,0.991290269,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.060062828,0.991290269,22318.01472,HMDB0004207,NA,NA,Amino acid metabolism,564327.7018,453694.181,556953.8078,498063.1018,515364.4088,628502.2242,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>glutamylthreonine,TRUE,0.402122514,0.024244375,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.402122514,0.024244375,-1132909.773,HMDB0028829,NA,NA,Not assigned,4795702.951,4904795.036,4271330.64,3076087.768,3888294.301,3608717.241,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>glutathione,TRUE,-0.625207554,0.001054876,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.625207554,0.001054876,1002910819,HMDB0000125,C00051,Glutathione,Glutathione metabolism,1984845939,1865886586,1696006067,2991259609,2849597130,2714614309,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>glutathione oxidized,TRUE,-1.075124874,2.57718719441913e-5,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.075124874,2.57718719441913e-5,3909340.944,HMDB0003337,C00127,Glutathione disulfide,Glutathione metabolism,3814316.636,3542508.43,3238509.557,7699334.092,7339262.453,7284760.909,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Gly-Gly,TRUE,-0.836095993,4.83003210444144e-5,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.836095993,4.83003210444144e-5,836742.9569,HMDB0011733,C02037,N-Glycylglycine,Amino acid metabolism,1041029.801,1087986.744,1067860.937,1735100.193,1856919.051,2115087.109,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>glyceraldehyde 3-phosphate,TRUE,0.051849975,0.979520749,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.051849975,0.979520749,-663679.4984,HMDB0001112,C00118,D-Glyceraldehyde3-phosphate,Glycolysis / Gluconeogenesis,17275062.52,17447470.12,21678424.24,17854683.82,17626646.95,18928587.62,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>glycerol 3-phosphate,TRUE,-0.526574362,0.020575146,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.526574362,0.020575146,6587011.626,HMDB0000126,C00093,sn-Glycerol 3-phosphate,Glycerophospholipid metabolism,14136524.96,15023970.19,15699491.92,19833236.97,22780687.67,22007097.32,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>glycerophosphocholine,TRUE,0.157820576,0.688452919,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.157820576,0.688452919,-1139100903,HMDB0000086,C00670,sn-Glycero-3-phosphocholine,Glycerophospholipid metabolism,9967473588,11680704505,11330421027,8863157096,9516495700,11181643614,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>glycerophosphoethanolamine,TRUE,-0.893225927,4.34371726443228e-6,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.893225927,4.34371726443228e-6,149057500.5,HMDB0000114,C01233,sn-Glycero-3-phosphoethanolamine,Glycerophospholipid metabolism,161574822.3,187556157.2,172459713.9,343422035,308364353.5,316976806.4,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>glycerophosphoinositol,TRUE,-1.515489545,6.93399e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.515489545,6.93399e-4,58320429.57,HMDB0011649,C01225,sn-Glycero-3-phospho-1-inositol,Not assigned,32379637.4,39548178.97,22190106.91,106750581.3,86435401.62,75893229.05,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>glycerylphosphorylcholine,FALSE,NA,NA,No Change,Not Detected,TRUE,-32.195065643248,0.39445522534372,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-32.195065643248,0.39445522534372,4916776543.080931,-4916776543.08094,Consumed,-7.26431608200073e-06,Consumed,Consumed,Consumed,-6972520756.291056,-2729863667.4934535,-1697671545.2160504,-8954116987.826849,-4229709758.577273,-4979778903.997616,4288717655.989417,-126511051.47544834,817572299.483618,HMDB0252858,NA,NA,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>glycine,TRUE,-2.757094503,5.37918265486326e-10,DOWN,DOWN,TRUE,-27.4577755140887,0.7448333390688353,No Change,Not Significant,TRUE,Intra DOWN + core Not Significant_Consumed,None,None,-2.757094503,5.37918265486326e-10,20061027.73,HMDB0000123,C00037,Glycine,Amino acid metabolism,3493625.64,3528048.525,3426172.144,24401002.44,23659708.25,22570218.81,DOWN,-27.4577755140887,0.7448333390688353,184337648.8520648,-184337648.852065,Consumed,-2.3283064365387e-09,Consumed,Consumed,Consumed,-381169106.7277118,-300498518.8245854,209481282.88246927,-268434949.06187686,-181066952.52862027,5946090.445294289,68513034.53622884,-138394033.669556,63934908.68803286,HMDB0000123,C00037,Glycine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GMP,TRUE,-0.009349094,0.999994869,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.009349094,0.999994869,10269.92955,HMDB0001397,C00144,GMP,Purine metabolism,1834825.431,1145320.587,1758844.229,2017508.512,1281797.722,1470493.801,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>GTP,TRUE,0.014736802,0.999986956,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.014736802,0.999986956,-75958.23088,HMDB0001273,C00044,GTP,Purine metabolism,8639229.594,4781881.143,9001367.461,10151090.29,5734975.388,6308537.825,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>guanosine,TRUE,0.161594218,0.977521855,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.161594218,0.977521855,-79792.34816,HMDB0000133,C00387,Guanosine,Purine metabolism,723508.8541,550655.7819,984889.1574,645845.029,644836.9206,728994.7992,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>hexanoylcarnitine C6,TRUE,-0.636617081,0.009138041,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.636617081,0.009138041,2027790.36,NA,NA,NA,NA,3730170.536,3893996.496,3343197.822,5003534.183,6791551.74,5255650.012,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>hexenoylcarnitine C6:1,TRUE,0.166220299,0.759687162,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.166220299,0.759687162,-199756.3317,NA,NA,NA,Fatty acyl carnitines,2009538.609,2011365.847,1485787.104,1481233.706,1995033.057,1431155.803,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>hexosamine phosphate,TRUE,-1.413775302,6.38719583659908e-5,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.413775302,6.38719583659908e-5,8723181.779,NA,NA,NA,Not assigned,4843648.51,5422672.645,5457406.837,16270968.81,13739096.58,11883207.94,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>hippuric acid-d5,TRUE,0.439568281,0.00783329,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.439568281,0.00783329,-1153822768,NA,NA,NA,NA,4624712907,4340353963,4214210391,3171399130,3180479423,3365930405,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>histidine,TRUE,-0.634005865,1.55023388056508e-5,No Change,Significant Negative,TRUE,-36.6318716634067,0.06789699916730108,No Change,Not Significant,TRUE,Intra Significant Negative + core Not Significant_Consumed,None,None,-0.634005865,1.55023388056508e-5,254577845.8,HMDB0000177,C00135,L-Histidine,Amino acid metabolism,482678795.8,445543238,455684105.6,737541468.7,692348663.2,717749545,Significant Negative,-36.6318716634067,0.06789699916730108,106485915244.45398,-106485915244.454,Consumed,-5.96046447753906e-07,Consumed,Consumed,Consumed,-105170590970.09071,-148751027110.83755,-72768817924.52927,-120694264061.49892,-85044876155.31361,79963989966.51,-3735227929.2185693,-97146881001.17952,20918118963.888092,HMDB0000177,C00135,L-Histidine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>homoarginine,TRUE,0.396349696,0.057005468,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.396349696,0.057005468,-513177.1297,HMDB0000670,C01924,L-Homoarginine,Arginine and proline metabolism,2012436.027,2134081.503,2262274.942,1595295.732,1435407.954,1838557.398,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>hydroxyphenyllactic acid,FALSE,NA,NA,No Change,Not Detected,TRUE,-29.0629301109131,0.006686550950649739,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-29.0629301109131,0.006686550950649739,560807386.6289225,-560807386.628923,Consumed,-2.3283064365387e-07,Consumed,Consumed,Consumed,-811248805.8502733,-890421054.4416394,-359874404.28621715,-46561366.97842655,-695931301.5880572,-165020090.00101334,34013946.19022758,-38320249.870490305,169326393.68127513,HMDB0000755,C03672,3-(4-Hydroxyphenyl)lactate,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>hydroxyphenylpyruvate,FALSE,NA,NA,No Change,Not Detected,TRUE,-27.9333886271077,1.5236700789955648e-12,No Change,Significant Negative,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-27.9333886271077,1.5236700789955648e-12,256323165.19236037,-256323165.19236,Consumed,6.98491930961609e-10,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-268054026.1829607,-232223403.9739017,-240942527.04673418,-258244706.61366335,-282151162.1445422,-37785710.19663984,-5715333.673239382,36348621.992890716,7152421.8769885125,NA,NA,NA,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>hydroxyproline,FALSE,NA,NA,No Change,Not Detected,TRUE,-34.985576399656,0.013670069240224847,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-34.985576399656,0.013670069240224847,34017932251.445896,-34017932251.4459,Consumed,1.48564577102661e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-34300129461.482346,-37602156792.32155,-13513059235.69228,-58010087820.00471,-26664227947.7285,3545542157.7586107,-14136854480.657732,-251977167.79064816,10843289490.689829,HMDB0000725,C01157,L-Hydroxyproline,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>hypotaurine,TRUE,0.799849514,5.03112e-4,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.799849514,5.03112e-4,-633113.2022,HMDB0000965,C00519,Hypotaurine,Not assigned,1469642.841,1469085.18,1524101.336,1028281.131,807591.0818,727617.5377,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>hypoxanthine,TRUE,-0.169970222,0.995358853,No Change,Not Significant,TRUE,-28.8776328571083,1.6993751739136087e-8,DOWN,DOWN,TRUE,Intra Not Significant + core DOWN_Released/Consumed,core_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.169970222,0.995358853,461455.4326,HMDB0000157,C00262,Hypoxanthine,Purine metabolism,6468141.648,2581735.886,2021929.459,2307248.109,2125909.147,8023016.036,Not Significant,-28.8776328571083,1.6993751739136087e-8,493212067.22042054,-493212067.22042,Consumed,3.72529029846191e-09,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-434665840.8338401,-566307743.1371487,-480189682.3276727,-411481273.1588421,-573415796.6445987,-95308552.50954095,-111726193.83483528,109364407.35566413,97670338.9887121,HMDB0000157,C00262,Hypoxanthine,Purine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IMP,TRUE,1.039883625,0.018119368,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.039883625,0.018119368,-442927.5093,HMDB0000175,C00130,IMP,Purine metabolism,775510.003,1009287.65,802228.0328,489397.0294,402330.883,366515.2455,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>indole,TRUE,-0.590224427,2.37248e-4,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.590224427,2.37248e-4,311820.5774,HMDB0000738,C00463,Indole,Not assigned,613402.132,620355.3958,616879.5372,991255.5537,847496.2107,947347.0326,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>indole-3-lactate,TRUE,-0.790122931,0.005443341,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.790122931,0.005443341,231940.378,HMDB0000671,C02043,Indolelactate,Not assigned,331840.8233,254852.3449,367503.6644,635862.5788,500994.7759,513160.6119,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>inosine,TRUE,-0.196935372,0.847103765,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.196935372,0.847103765,100878.5567,HMDB0000195,C00294,Inosine,Purine metabolism,601369.9961,781272.9123,686507.5145,719841.5179,620400.6136,1031543.961,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>isoleucine,TRUE,-0.27385293,0.073462643,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.27385293,0.073462643,85393372.79,HMDB0000172,C00407,L-Isoleucine,Valine, leucine and isoleucine biosynthesis,420406029.8,401997946.1,403148115.6,470955902.5,462226339.1,548549968.2,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>isovalerylcarnitine,TRUE,0.917047368,0.006503844,UP,UP,TRUE,-29.588281426066,0.18628972561682122,No Change,Not Significant,TRUE,Intra UP + core Not Significant_Released/Consumed,None,None,0.917047368,0.006503844,-14510266.29,HMDB0000688,C20826,Isovalerylcarnitine,Fatty acyl carnitines,29656655.78,30619593.76,32262096.75,19753215.06,15537391.2,13716941.17,UP,-29.588281426066,0.18628972561682122,807161110.9191858,-807161110.919185,Consumed,7.45058059692383e-09,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-697229665.0016221,-118424171.89205277,-456086778.24297774,-818021579.3977549,-1946043360.0615187,-248888938.3161011,-85280361.19713396,416227956.8510329,-82058657.33779782,HMDB0000688,C20826,Isovalerylcarnitine,Fatty acyl carnitines</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>KMV,TRUE,0.17062961,0.906374864,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.17062961,0.906374864,-530653.0839,NA,NA,NA,Valine, leucine and isoleucine biosynthesis,4475373.167,4746638.363,5049872.57,3605000.644,2919326.03,6155598.175,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>KMV+KIC,FALSE,NA,NA,No Change,Not Detected,TRUE,-29.6344864485061,0.9954766474134331,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-29.6344864485061,0.9954766474134331,833430379.7932488,-833430379.793241,Consumed,1.19209289550781e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,151430198.9162137,-1872610824.2051704,-1126653130.6296005,-1151221255.1693628,-168096887.8782848,-3073634444.2861533,-2211480934.345639,7928553306.211556,-2643437927.5797634,NA,NA,NA,Valine, leucine and isoleucine biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>lactate,TRUE,0.301584319,0.164140697,No Change,Not Significant,TRUE,36.9695605010558,0.8641564994783861,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released,None,None,0.301584319,0.164140697,-134441906.7,HMDB0000190,C00186,(S)-Lactate,Glycolysis / Gluconeogenesis,721790169.7,654376726.9,761914316.9,565048879.4,499136449.8,670570164.3,Not Significant,36.9695605010558,0.8641564994783861,-134569499554.92346,134569499554.924,Released,0.000244140625,Released,Released,Released,97590888277.5189,206867908395.51202,190310119512.25168,103170013479.702,74908568109.63596,-284483048397.33734,-179049946510.2211,561266645134.7952,-97733650227.23575,HMDB0000190,C00186,(S)-Lactate,Glycolysis / Gluconeogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>leucine,TRUE,-0.454218845,0.002871952,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.454218845,0.002871952,160435321,HMDB0000687,C00123,L-Leucine,Valine, leucine and isoleucine biosynthesis,452768187.2,414521702.4,433393651.7,577249919.7,564558365.3,640181219.3,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>leucine+isoleucine,FALSE,NA,NA,No Change,Not Detected,TRUE,-37.9684296371823,3.0425273411793796e-10,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-37.9684296371823,3.0425273411793796e-10,268928115793.0837,-268928115793.083,Consumed,5.91278076171875e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-259194808261.49313,-242686616304.33206,-293272846439.57434,-280956937524.223,-268529370435.79456,-58640812488.026505,-36322079822.318436,135899646822.98074,-40936754512.63557,NA,NA,NA,Valine, leucine and isoleucine biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>linoleic acid,FALSE,NA,NA,No Change,Not Detected,TRUE,-27.3210604206957,4.951594689828198e-14,No Change,Significant Negative,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-27.3210604206957,4.951594689828198e-14,167671287.81100804,-167671287.811008,Consumed,7.45058059692383e-09,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-180609551.6812588,-143761221.57060856,-190368872.36933655,-168696549.27828434,-154920244.1555518,-14113831.923910795,-12615581.672115814,18738716.291623026,7990697.304403612,HMDB0000673,C01595,Linoleate,Fatty acid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>lysine,TRUE,0.400610359,0.07719657,No Change,Not Significant,TRUE,31.8136555662736,0.9999973373973502,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released,None,None,0.400610359,0.07719657,-9550961.352,HMDB0000182,C00047,L-Lysine,Amino acid metabolism,39846551.36,37827659.2,40500396.47,27919226.33,25870671,35731825.65,Not Significant,31.8136555662736,0.9999973373973502,-3774544911.24537,3774544911.24537,Released,3.02791595458984e-05,Released,Released,Released,13696479742.845415,11743468238.906364,-59683465021.921104,8790269555.970701,44325972040.42549,3694637940.379678,44899902987.32562,-35719065763.92516,-12875475163.780016,HMDB0000182,C00047,L-Lysine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>malate,TRUE,0.098135218,0.749863688,No Change,Not Significant,TRUE,-31.1120474135274,0.9999967828775342,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released/Consumed,None,None,0.098135218,0.749863688,-144218237.7,HMDB0000156,C00149,(S)-Malate,Citrate cycle (TCA cycle),2244208988,2276823115,2058245048,1940397414,2064435997,2141789027,Not Significant,-31.1120474135274,0.9999967828775342,2320916403.4840326,-2320916403.48408,Consumed,2.38418579101562e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,9615953289.851751,-2676078805.8241806,-13402412396.831945,-17210125423.70258,12068081319.08655,26741554548.773746,37018750512.03025,-61292460530.75885,-2467844530.045146,HMDB0000156,C00149,(S)-Malate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>malonate,TRUE,0.170114297,0.768843429,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.170114297,0.768843429,-816248.0861,HMDB0000691,C00383,Malonate,Pyrimidine metabolism,7457169.618,8327513.223,6230907.718,5918003.152,6198577.345,7450265.804,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>malonylcarnitine C3-DC,TRUE,2.953720686,7.31572621371912e-5,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,2.953720686,7.31572621371912e-5,-1372270.779,HMDB0002095,NA,NA,Fatty acyl carnitines,1553685.496,1689016.824,1484239.049,268572.0402,143914.9542,197642.0372,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>mesaconate,TRUE,1.026183305,5.32270411566227e-5,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.026183305,5.32270411566227e-5,-17145852.66,HMDB0000749,C01732,Mesaconate,Citrate cycle (TCA cycle),32929422.8,35011520.19,33116633.78,14951797.29,16354894.21,18313327.27,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>methionine,TRUE,-0.896409581,4.40890136513827e-5,DOWN,DOWN,TRUE,-36.2702934145275,5.88418203051333e-14,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-0.896409581,4.40890136513827e-5,69608541.77,HMDB0000696,C00073,L-Methionine,Amino acid metabolism,85256547.89,77161399.86,80000104.77,144315072.6,146980149,159948456.2,DOWN,-36.2702934145275,5.88418203051333e-14,82879337203.33995,-82879337203.34,Consumed,2.23517417907715e-08,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-81013655097.30876,-75024885917.166,-88725803798.42584,-87791214163.3691,-81841127040.4301,-7444471180.539031,201034005.0103403,11358383920.942343,-4114946745.413652,HMDB0000696,C00073,L-Methionine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>methionine sulfoxide,TRUE,-0.557836742,0.01104194,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.557836742,0.01104194,203422.6657,HMDB0002005,C02989,L-MethionineS-oxide,Cysteine and methionine metabolism,539805.6646,422230.5195,330739.4067,617546.5113,623903.4048,661593.6717,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>methylarginine,FALSE,NA,NA,No Change,Not Detected,TRUE,32.5549906622257,0.5428776446670375,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,32.5549906622257,0.5428776446670375,-6309990390.997943,8841424460.94593,Released,2531434069.948,Released,Released,Released,12684633648.103819,9085197459.604176,103813135.92851111,10076456256.798323,12257021804.294834,6988128733.813481,10125736279.792004,-6524943070.977505,-463185662.83597517,HMDB0250980,NA,NA,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>methylaspartate,FALSE,NA,NA,No Change,Not Detected,TRUE,32.3817786672638,0.9937687117353382,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,32.3817786672638,0.9937687117353382,-5596115787.924288,5596115787.92422,Released,-2.95639038085938e-05,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,4214127690.521964,2563881735.3835497,1179622663.3059187,14157297089.175121,5865649761.234543,15719674092.892714,15032311401.82486,-21217737352.890068,-9534248141.827623,HMDB0002393,C12269,N-Methyl-D-aspartic acid,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>methylhistidine,TRUE,-0.325416252,0.010596341,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.325416252,0.010596341,9267680.207,HMDB0000001,C01152,N(pi)-Methyl-L-histidine,Amino acid metabolism,37194008.99,36330172.34,36358004.82,46537469.42,43426917.52,47720839.83,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>methylindole,TRUE,-0.414013606,1.51894e-4,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.414013606,1.51894e-4,676412.4514,HMDB0000466,C08313,Skatole,Not assigned,1940466.404,2066645.513,2097925.19,2724280.199,2607979.061,2802015.201,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>methylmalonylcarnitine C3-DC-M/succinylcarnitine C4-DC,TRUE,2.419830756,2.08158955627979e-8,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,2.419830756,2.08158955627979e-8,-37595579.42,NA,NA,NA,Fatty acyl carnitines,48024086.07,44890301.49,45793886.28,9423708.801,8611878.675,7885948.092,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>mevalonic acid 5-pyrophosphate,TRUE,0.242965459,0.98162312,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.242965459,0.98162312,-50093.05019,NA,NA,NA,Not assigned,426519.1344,250685.148,292380.0073,344295.7788,168581.4658,306427.8945,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>myo-inositol,TRUE,1.666314831,2.10689370405692e-6,UP,UP,TRUE,32.9462932323802,0.23957123216678322,No Change,Not Significant,TRUE,Intra UP + core Not Significant_Released/Consumed,None,None,1.666314831,2.10689370405692e-6,-178200831.1,HMDB0000211,C00137,myo-Inositol,Not assigned,268277701.4,260066393.6,252162547.8,91206977.84,80653826.89,74043344.73,UP,32.9462932323802,0.23957123216678322,-8276038624.975198,8276038624.97518,Released,-2.38418579101562e-07,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,4483835150.407816,8188082914.204562,9629754059.443966,12486714559.198204,6591806441.621355,7312929712.728005,4445686917.274802,-18085456373.315502,6326839743.312694,HMDB0000211,C00137,myo-Inositol,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>N-acetylalanine,TRUE,-0.470900753,1.36266176237188e-5,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.470900753,1.36266176237188e-5,4955448.789,HMDB0000766,NA,NA,Amino acid metabolism,12143217.01,13214624.54,13158549.92,18445570.28,17684057.45,17253110.11,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>N-acetylarginine,TRUE,-2.358075573,6.06212969933573e-7,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-2.358075573,6.06212969933573e-7,2045855.762,HMDB0004620,NA,NA,Amino acid metabolism,495265.0773,365013.6412,626945.6879,2833531.344,2380366.854,2410893.495,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>N-acetylaspartate,TRUE,-5.471270942,5.1625370645069804e-14,DOWN,DOWN,TRUE,-36.1726005666681,2.9976021664879227e-14,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-5.471270942,5.1625370645069804e-14,2700125216,HMDB0000812,C01042,N-Acetyl-L-aspartate,Alanine, aspartate and glutamate metabolism,59680626.65,62471731.77,64653364.01,2717445462,2788055498,2781680410,DOWN,-36.1726005666681,2.9976021664879227e-14,77452919338.97089,-77452919338.9708,Consumed,1.78813934326172e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-77025900220.52109,-77424185980.44182,-77721799640.22699,-77708373116.3265,-77384337737.33783,-5683746441.585672,1195389604.3015845,6236626744.864468,-1748269907.5803726,HMDB0000812,C01042,N-Acetyl-L-aspartate,Alanine, aspartate and glutamate metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>N-acetylaspartylglutamate,TRUE,-8.160773493,1.88238313825195e-12,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-8.160773493,1.88238313825195e-12,69385394.2,HMDB0001067,C12270,N-Acetylaspartylglutamate,Alanine, aspartate and glutamate metabolism,280252.8128,230783.4055,218878.1725,66586131.56,70708615.03,71591350.42,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>N-acetylglutamate,TRUE,-1.742348048,2.9265182954763e-7,DOWN,DOWN,TRUE,-30.8154720348604,1.9606538614880265e-13,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-1.742348048,2.9265182954763e-7,87329027.16,HMDB0001138,C00624,N-Acetyl-L-glutamate,Amino acid metabolism,35106202.1,38486887.1,38090728.73,113692991.1,125423252.3,134554656.1,DOWN,-30.8154720348604,1.9606538614880265e-13,1889650179.334308,-1889650179.33431,Consumed,1.13621354103088e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-1884367551.0378196,-1741102504.4019961,-2036063291.2365568,-1944323492.860089,-1842394057.1350815,-49761950.3384529,129234294.40224536,-121878694.23224321,42406350.168451205,HMDB0001138,C00624,N-Acetyl-L-glutamate,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>N-acetylglutamine,TRUE,-1.970655579,4.17587597834057e-9,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.970655579,4.17587597834057e-9,9707976.216,HMDB0006029,NA,NA,Amino acid metabolism,3339694.841,3555700.745,3080391.137,12373728.9,13474542.33,13251444.14,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>N-acetylhexosamine phosphate,TRUE,0.881941615,1.63247e-4,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.881941615,1.63247e-4,-1550904.93,NA,NA,NA,Not assigned,3492747.684,3101910.139,3578248.998,1982760.494,1792756.508,1744675.031,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>N-acetylhistidine,TRUE,-0.313218674,0.72142723,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.313218674,0.72142723,2837600.756,HMDB0032055,C02997,N-Acetyl-L-histidine,Amino acid metabolism,13576648.38,9667282.724,11863796.72,11759960.36,12170531.04,19690038.69,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>N-acetylmethionine,TRUE,-1.346358787,1.21677923691221e-5,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.346358787,1.21677923691221e-5,31951061.61,HMDB0011745,C02712,N-Acetylmethionine,Amino acid metabolism,18838959.93,20112930.57,23181677.42,48453786.27,51397524.14,58135442.34,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>N-acetylneuramic acid,TRUE,1.375952694,1.04722e-4,UP,UP,TRUE,-28.6581141650408,0.7036228364347776,No Change,Not Significant,TRUE,Intra UP + core Not Significant_Released/Consumed,None,None,1.375952694,1.04722e-4,-10808241.65,HMDB0000230,C19910,N-Acetyl-beta-neuraminate,Not assigned,19176828.39,15346443.84,18225433.45,5670631.961,7010638.579,7642710.177,UP,-28.6581141650408,0.7036228364347776,423596129.1488234,-423596129.148822,Consumed,4.61935997009277e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,205146001.90706825,-683419365.2265139,-174610307.18444163,-653308225.9819876,-811788749.2582369,-687775477.2707164,174406220.73245472,751634309.4062458,-238265052.86798227,HMDB0000230,C19910,N-Acetyl-beta-neuraminate,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>N-acetylornithine,TRUE,-0.33563674,0.003363624,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.33563674,0.003363624,3217616.476,NA,NA,NA,Amino acid metabolism,12457407.56,11974256.96,12420520.95,15951194.51,14801961.59,15751878.79,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>N-acetylserine,TRUE,-0.772232811,2.47697593735996e-6,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.772232811,2.47697593735996e-6,220040186.1,HMDB0002931,NA,NA,Amino acid metabolism,296327772.5,316541222.6,319621872.9,566201699.2,524160845.6,502248881.4,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>N-carbamoylaspartate,TRUE,-0.184392044,0.998433312,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.184392044,0.998433312,1115114.619,HMDB0000828,C00438,N-Carbamoyl-L-aspartate,Pyrimidine metabolism,7067282.049,9521686.252,7948163.373,6458638.532,17592657.98,3831179.014,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>NAD,TRUE,0.121362538,0.098641693,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.121362538,0.098641693,-15497882.42,HMDB0000902,C00003,NAD+,Oxidative phosphorylation,183694476.5,195229607.3,197341044,178563109.1,180711542.8,170496828.6,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>NADH,TRUE,-0.213190433,0.950140641,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.213190433,0.950140641,217814.6264,HMDB0001487,C00004,NADH,Oxidative phosphorylation,1465478.247,1182152.381,1455654.432,2631484.086,1014651.853,1110593,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>NADP,TRUE,-0.293705377,0.745748849,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.293705377,0.745748849,220780.0127,HMDB0304435,C00006,NADP+,Glutathione metabolism,1048696.083,866394.5614,1018414.591,1153277.545,1395012.63,1047555.099,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>NADPH,TRUE,0.78312386,0.397612529,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.78312386,0.397612529,-1052147.236,HMDB0000221,C00005,NADPH,Glutathione metabolism,2990974.644,1464519.806,3079706.488,2108319.371,812000.8196,1458439.041,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>oleic acid,FALSE,NA,NA,No Change,Not Detected,TRUE,-31.9691673652389,1.635518942499914e-9,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-31.9691673652389,1.635518942499914e-9,4204151069.684241,-4204151069.68424,Consumed,-4.32133674621582e-07,Consumed,Consumed,Consumed,-4462496898.969814,-2710151138.214778,-4675611440.789551,-4560817453.698374,-4611678416.748681,-952876539.1597285,-819992891.2924575,1560318665.0926874,212550765.3594969,HMDB0000207,C00712,(9Z)-Octadecenoic acid,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ophthalmate,TRUE,-1.191825841,1.15605724659851e-7,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.191825841,1.15605724659851e-7,97646648.03,HMDB0005765,C21016,Ophthalmate,Cysteine and methionine metabolism,73393577.11,80105921.95,74572856.49,174027560.6,181840397.4,165144341.6,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ornithine,TRUE,-1.367637323,1.23009813013386e-6,DOWN,DOWN,TRUE,-34.5564728950927,9.389709006490943e-5,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-1.367637323,1.23009813013386e-6,3482754.274,HMDB0000214,C00077,L-Ornithine,Amino acid metabolism,2340577.833,2212177.262,2058077.031,5279053.998,5976593.188,5803447.761,DOWN,-34.5564728950927,9.389709006490943e-5,25265906565.883396,-25265906565.8834,Consumed,3.33786010742188e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-21731478015.302227,-25037441006.833637,-34664953401.72579,-24872176029.534084,-20023484376.02117,-10324686953.773981,13806291633.899055,4506260102.645232,-7987864782.770293,HMDB0000214,C00077,L-Ornithine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>orotate,TRUE,-1.123705384,0.927461789,No Change,Not Significant,TRUE,31.8302930646795,2.9976021664879227e-14,UP,UP,TRUE,Intra Not Significant + core UP_Released/Consumed,core_UP (Released/Consumed),core_UP (Released/Consumed),-1.123705384,0.927461789,48858811.98,HMDB0000226,C00295,Orotate,Pyrimidine metabolism,33675553.28,45159952.57,45480929.92,35894670.35,191346122.2,43652079.21,Not Significant,31.8302930646795,2.9976021664879227e-14,-3818325811.2073703,3818325811.20737,Released,-3.25962901115417e-09,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,4038223215.6643376,3866064639.6220903,3600500069.271825,3873170632.8521233,3713670498.6264668,-77084021.43058828,-129707766.2755702,200398414.2955605,6393373.410597952,HMDB0000226,C00295,Orotate,Pyrimidine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>orotidine,TRUE,2.557279938,3.07217348963773e-5,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,2.557279938,3.07217348963773e-5,-1054203699,HMDB0000218,C01103,Orotidine 5'-phosphate,Pyrimidine metabolism,1276466724,1343400921,1190027768,321761909,192657636,132864772.7,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>palmitate,FALSE,NA,NA,No Change,Not Detected,TRUE,-33.0016685615671,3.130011838603508e-8,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-33.0016685615671,3.130011838603508e-8,8599875103.263119,-8599875103.26311,Consumed,-1.86264514923096e-09,Consumed,Consumed,Consumed,-9334208165.51682,-7997462431.754894,-9075712770.178177,-9901827240.693316,-6690164908.17236,-1422596268.514262,-1777716071.6772227,3168004297.581064,32308042.610420458,HMDB0000220,C00249,Hexadecanoic acid,Fatty acid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>pantothenate,TRUE,0.581519846,4.24714e-4,No Change,Significant Positive,TRUE,-30.2775783257819,0.9995080805444101,No Change,Not Significant,TRUE,Intra Significant Positive + core Not Significant_Consumed,None,None,0.581519846,4.24714e-4,-446705298.3,HMDB0000210,C00864,Pantothenate,Vitamin digestion and absorption,1289689777,1392441377,1357518914,784232784.1,963576666.3,951724722.6,Significant Positive,-30.2775783257819,0.9995080805444101,1301545251.728768,-1301545251.72879,Consumed,-1.47819519042969e-05,Consumed,Consumed,Consumed,-2367121445.527412,-65298803.46143864,-2038385595.238856,-6281120217.709953,4244199803.2937074,2444512083.3661976,4253436186.490527,-11974483508.724691,5276535238.867908,HMDB0000210,C00864,Pantothenate,Vitamin digestion and absorption</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>pentose phosphates,TRUE,0.145495704,0.389155593,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.145495704,0.389155593,-732340.8239,NA,NA,NA,Not assigned,7125490.371,8110977.206,7665570.104,6149509.275,7199587.684,7355918.251,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>phenylalanine,TRUE,-0.452668449,0.002882826,No Change,Significant Negative,TRUE,-37.3016303476272,6.940808794375641e-7,DOWN,DOWN,TRUE,Intra Significant Negative + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.452668449,0.002882826,89202651.46,HMDB0000159,C00079,L-Phenylalanine,Amino acid metabolism,246346088.2,238982768.6,240743506.3,324858634.3,307224248.3,361597434.8,Significant Negative,-37.3016303476272,6.940808794375641e-7,169398523953.54944,-169398523953.549,Consumed,6.00814819335938e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-138730087696.72855,-183019882629.54422,-176280142813.37503,-172141345612.3201,-176821161015.77856,-37037474068.073204,-29337507442.986485,112028245720.25409,-45653264209.19416,HMDB0000159,C00079,L-Phenylalanine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>phosphocholine,FALSE,NA,NA,No Change,Not Detected,TRUE,-32.7996703382479,2.9976021664879227e-14,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-32.7996703382479,2.9976021664879227e-14,7476263845.498447,-7476263845.49844,Consumed,2.38418579101562e-07,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-7477398196.271826,-7507162824.035986,-7766083171.489989,-7595448653.851283,-7035226381.843122,-352406048.52442503,248068992.61827162,-54667177.292248875,159004233.19840324,NA,NA,NA,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>phosphocreatine,TRUE,-6.977943827,1.03678109431016e-8,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-6.977943827,1.03678109431016e-8,413931706,HMDB0001511,C02305,Phosphocreatine,Arginine and proline metabolism,4762172.829,2805519.519,2362061.478,406842317.8,454666369.4,390216184.7,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>phosphoenolpyruvate,TRUE,1.073839039,0.001686023,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.073839039,0.001686023,-7974642.056,HMDB0000263,C00074,Phosphoenolpyruvate,Citrate cycle (TCA cycle),17540594.32,14936661.92,13096744.25,7641795.01,7345260.803,6663018.507,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>phosphoethanolamine,TRUE,-6.152477645,1.50674183130306e-8,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-6.152477645,1.50674183130306e-8,117999163.5,HMDB0000224,C00346,Ethanolamine phosphate,Glycerophospholipid metabolism,1446896.442,1850009.153,1750502.757,125645043.5,125093590,108306265.2,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>phosphorylcholine,TRUE,-1.627422046,5.13770708310268e-7,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.627422046,5.13770708310268e-7,12590823768,HMDB0001565,C00588,Choline phosphate,Glycerophospholipid metabolism,5942313850,6306919385,5827142531,19791526161,19083497903,16973823007,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>proline,TRUE,-0.711668609,4.50730472389971e-7,No Change,Significant Negative,TRUE,36.5599524581073,0.4603557498260612,No Change,Not Significant,TRUE,Intra Significant Negative + core Not Significant_Released/Consumed,None,None,-0.711668609,4.50730472389971e-7,7804113600,HMDB0000162,C00148,L-Proline,Amino acid metabolism,11845789148,12405225701,12462870597,19570723886,20403301753,20152200608,Significant Negative,36.5599524581073,0.4603557498260612,-101307670679.97807,101307670679.978,Released,-0.000237464904785156,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,111642587069.44049,123843613016.8376,139089761756.4126,39035731627.31958,92926659929.87827,61996196709.97845,43452182821.562675,-75414860829.08322,-30033518702.45885,HMDB0000162,C00148,L-Proline,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>propionylcarnitine,TRUE,-0.07568367,0.880564694,No Change,Not Significant,TRUE,-32.2188208876962,2.316937445678846e-6,DOWN,DOWN,TRUE,Intra Not Significant + core DOWN_Released/Consumed,core_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.07568367,0.880564694,21838267.14,HMDB0000824,C03017,O-Propanoylcarnitine,Fatty acyl carnitines,386050764.5,385850667.6,444481897.6,495435267.5,409676534.5,376786329.1,Not Significant,-32.2188208876962,2.316937445678846e-6,4998405803.660118,-4998405803.66011,Consumed,3.71504575014114e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-6061846788.247342,-5133868488.916086,-4373779994.99164,-4971937425.343492,-4450596320.801994,-482917911.5400081,-1512424199.042421,2011076709.320792,-15734598.73834787,HMDB0000824,C03017,O-Propanoylcarnitine,Fatty acyl carnitines</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>pyroglutamic-acid,FALSE,NA,NA,No Change,Not Detected,TRUE,-34.4145589759757,0.7360823174251769,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-34.4145589759757,0.7360823174251769,22898895717.748226,-22898895717.7482,Consumed,-5.86509704589844e-05,Consumed,Consumed,Consumed,3518820820.178986,-20306669878.438168,-43324864909.69625,-9026594214.680813,-45355170406.10475,-11372947061.724617,-12995628535.603758,47814816424.39841,-23446240827.070267,HMDB0000267,C01879,5-Oxoproline,Glutathione metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>pyroglutamic acid,TRUE,0.139065873,0.72048127,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.139065873,0.72048127,-32380479.14,HMDB0000267,C01879,Pyroglutamic acid,Glutathione metabolism,379771328.7,331154954.6,346187837.8,274178849.3,290280210.4,395513624,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>pyruvate,TRUE,0.495609413,0.139508673,No Change,Not Significant,TRUE,34.7199005760319,1.4311392443211446e-4,UP,UP,TRUE,Intra Not Significant + core UP_Released,core_UP (Released),core_UP (Released),0.495609413,0.139508673,-7120368.16,HMDB0000243,C00022,Pyruvate,Glycolysis / Gluconeogenesis,22840327.69,23703684.36,26927998.69,16538688.65,14243087.05,21329130.56,Not Significant,34.7199005760319,1.4311392443211446e-4,-28296421747.907734,28296421747.9078,Released,7.62939453125e-06,Released,Released,Released,34085075195.564526,25951864680.35385,22724919064.539288,31760520227.13974,26959729571.94141,-8525079495.24927,-9095235612.109156,25472901354.49395,-7852586247.135493,HMDB0000243,C00022,Pyruvate,Glycolysis / Gluconeogenesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>S-(2-succinyl)cysteine,TRUE,-2.385838082,3.73147e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-2.385838082,3.73147e-4,461895.488,NA,NA,NA,Not assigned,90757.83575,121873.438,115227.4409,689607.3618,614458.7425,409479.0743,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>S-adenosylhomocysteine,TRUE,-0.409725253,0.006389175,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.409725253,0.006389175,2394136.991,HMDB0000939,C00021,S-Adenosyl-L-homocysteine,Cysteine and methionine metabolism,6780883.87,7467058.854,7620795.453,10794289.9,9673118.945,8583740.303,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>S-adenosylmethionine,TRUE,1.039835172,5.44540889980683e-5,UP,UP,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,1.039835172,5.44540889980683e-5,-47679647.64,HMDB0001185,C00019,S-Adenosyl-L-methionine,Cysteine and methionine metabolism,89552281.38,92100460.15,96840676.76,39390303.21,48631184.92,47432987.26,UP,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>S-lactoylglutathione,TRUE,0.037418479,0.999467343,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.037418479,0.999467343,-24334.89461,HMDB0001066,C03451,(R)-S-Lactoylglutathione,Glutathione metabolism,880478.6497,1142299.753,828627.2031,1216146.276,952835.9794,609418.6674,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>sedoheptulose 7-phosphate,TRUE,-0.083758314,0.940093726,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.083758314,0.940093726,38073.82448,HMDB0258206,C05382,Sedoheptulose 7-phosphate,Pentose phosphate pathway,578935.4801,692476.1357,639437.9553,520206.0801,708811.9631,796053.0013,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>serine,TRUE,-2.553944836,2.88674225745744e-7,DOWN,DOWN,TRUE,-32.9179018083608,1.1168843627729075e-13,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-2.553944836,2.88674225745744e-7,40477616.84,HMDB0000187,C00065,L-Serine,Amino acid metabolism,9213418.426,8089039.967,7620248.873,52847766.34,50407160.72,43100630.72,DOWN,-32.9179018083608,1.1168843627729075e-13,8114762968.380907,-8114762968.38091,Consumed,1.85519456863403e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-8129992417.082857,-7675203627.61251,-8072758178.005888,-8852935960.46773,-7842924658.735543,-859365026.5611572,177980495.30494586,405193307.5943964,276191223.6618224,HMDB0000187,C00065,L-Serine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>stearic acid,FALSE,NA,NA,No Change,Not Detected,TRUE,-32.5991395199642,1.4787220968370818e-5,DOWN,DOWN,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-32.5991395199642,1.4787220968370818e-5,6506071448.932426,-6506071448.93242,Consumed,-4.4703483581543e-07,Consumed,Consumed,Consumed,-7674628350.479779,-6218644747.258514,-7388301551.286547,-6862720173.459657,-4386062422.177612,-1313777621.6456864,-2187956793.270608,2503923356.624134,997811058.2921585,HMDB0000827,C01530,Octadecanoic acid,Fatty acid biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>stearoylcarnitine C18,TRUE,0.300695468,0.948095366,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.300695468,0.948095366,-220525.9442,HMDB0000848,NA,NA,Fatty acyl carnitines,1189002.371,1122525.38,1204902.14,1850692.297,555442.3529,448717.4078,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>succinate,TRUE,-0.61834303,0.027738963,No Change,Significant Negative,TRUE,-32.5519173571145,0.003927770018746557,DOWN,DOWN,TRUE,Intra Significant Negative + core DOWN_Consumed,Both_DOWN (Consumed),core_DOWN (Consumed),-0.61834303,0.027738963,16408901.9,HMDB0000254,C00042,Succinate,Citrate cycle (TCA cycle),31488406.08,28513243.13,31991788.52,39546102.13,42678320.02,58995721.27,Significant Negative,-32.5519173571145,0.003927770018746557,6296562823.60477,-6296562823.60477,Consumed,-3.66568565368652e-06,Consumed,Consumed,Consumed,-9358235701.430796,-3545438081.7969646,-4490735039.486822,-8571780464.806791,-5516624830.50249,-829605058.9104091,1418206886.1287057,-2779579365.7580466,2190977538.5397353,HMDB0000254,C00042,Succinate,Citrate cycle (TCA cycle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>succinyladenosine,FALSE,NA,NA,No Change,Not Detected,TRUE,-25.9756053878972,0.4524365234678953,No Change,Not Significant,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,-25.9756053878972,0.4524365234678953,65983656.329823986,-65983656.3298239,Consumed,-2.88709998130798e-08,Consumed,Consumed,Consumed,-84879241.77213675,-34724235.761017665,-71816944.09412448,-85249014.50122923,-53248845.520611584,-80598679.40781274,-28964960.196444336,90525381.55360185,19038258.05065512,HMDB0000912,NA,NA,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>succinylglutathione,TRUE,-1.75231827,5.77695481006613e-5,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.75231827,5.77695481006613e-5,2462475.873,NA,C03174,S-Succinylglutathione,Glutathione metabolism,1205182.312,1074784.571,838413.5894,3953230.157,3574104.733,2978473.201,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>taurine,TRUE,1.096313926,4.72572350577183e-5,UP,UP,TRUE,-35.3137840721369,0.6740577352111854,No Change,Not Significant,TRUE,Intra UP + core Not Significant_Consumed,None,None,1.096313926,4.72572350577183e-5,-2058049338,HMDB0000251,C00245,Taurine,Not assigned,4065166566,3771464972,3762586211,2084269089,1693870941,1646929705,UP,-35.3137840721369,0.6740577352111854,42707904814.30518,-42707904814.3052,Consumed,-9.5367431640625e-07,Consumed,Consumed,Consumed,-55134873538.182144,-52666611436.66368,-50601723866.12516,-38926227747.56628,-16210087482.98878,74672054822.89774,-11462573451.641602,-36424797633.73357,-26784683737.52257,HMDB0000251,C00245,Taurine,Not assigned</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>tetradecanoylcarnitine C14,TRUE,-2.317980003,4.91017e-4,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-2.317980003,4.91017e-4,1566494.835,HMDB0005066,NA,NA,Not assigned,340557.0368,449592.8495,388748.4562,2529778.017,1826551.223,1522053.608,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>tetradecenoylcarnitine C14:1,TRUE,-1.031105881,0.225272392,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-1.031105881,0.225272392,617523.732,NA,NA,NA,Fatty acyl carnitines,657106.8235,518660.8133,599422.7586,818846.7027,1417977.909,1390936.98,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>thiamine,TRUE,-0.485096439,0.003013661,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.485096439,0.003013661,24768564.95,HMDB0000235,C00378,Thiamine,Vitamin digestion and absorption,62988916.27,61346153.43,61578164.61,86600447.81,82321788.85,91296692.5,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>threonine,TRUE,-1.917911799,5.11672753511494e-6,DOWN,DOWN,TRUE,-36.3496381855302,6.699249126551621e-7,DOWN,DOWN,TRUE,Intra DOWN + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),Both_DOWN (Released/Consumed),-1.917911799,5.11672753511494e-6,473890280.5,HMDB0000167,C00188,L-Threonine,Amino acid metabolism,172999611.6,171132446.5,167489062.7,735156746.1,636300014.2,561835202.2,DOWN,-36.3496381855302,6.699249126551621e-7,87565176093.68672,-87565176093.6867,Consumed,5.91278076171875e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-93625066652.13553,-65993933761.225006,-104209512956.64485,-96675995112.23224,-77321371986.1957,-12490581856.822964,-6672910201.351136,26591199850.22577,-7427707792.051433,HMDB0000167,C00188,L-Threonine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>trans-4-hydroxyproline,TRUE,-2.245688902,3.7611839988072e-6,DOWN,DOWN,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-2.245688902,3.7611839988072e-6,100131005.2,HMDB0000725,C01157,Hydroxyproline,Amino acid metabolism,28087442.39,27500982.3,24674010.64,144520544.3,126350663.8,109784243,DOWN,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>trimethyllysine,TRUE,-0.070584734,0.930911049,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.070584734,0.930911049,280349.0368,HMDB0001325,C03793,N6,N6,N6-Trimethyl-L-lysine,Amino acid metabolism,5723521.411,5150431.099,5899277.537,6238519.882,5118803.368,6256953.907,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>tryptophan,TRUE,-0.394982004,6.35126e-4,No Change,Significant Negative,TRUE,-37.1774915855229,1.3596402259619111e-7,DOWN,DOWN,TRUE,Intra Significant Negative + core DOWN_Released/Consumed,Both_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.394982004,6.35126e-4,80212939.77,HMDB0000929,C00078,L-Tryptophan,Amino acid metabolism,256797971.1,253882481,253430945.4,342974414.4,316408141.5,345367661,Significant Negative,-37.1774915855229,1.3596402259619111e-7,155431891028.07327,-155431891028.073,Consumed,1.43051147460938e-06,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-127422894031.43846,-140904067241.64246,-180457790105.09247,-172521140176.01346,-155853563586.17896,-42343649932.684975,-4735406623.146227,61104148706.43085,-14025092150.59964,HMDB0000929,C00078,L-Tryptophan,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>tyrosine,TRUE,-0.220277814,0.204166403,No Change,Not Significant,TRUE,-37.0125505882413,1.1335343119700525e-7,DOWN,DOWN,TRUE,Intra Not Significant + core DOWN_Consumed,core_DOWN (Consumed),core_DOWN (Consumed),-0.220277814,0.204166403,19234289.09,HMDB0000158,C00082,L-Tyrosine,Amino acid metabolism,119090610.5,122771462.6,107941535.1,141284064.8,125795316.8,140427093.8,Not Significant,-37.0125505882413,1.1335343119700525e-7,138639806350.2861,-138639806350.286,Consumed,-2.86102294921875e-05,Consumed,Consumed,Consumed,-143040650638.71347,-123320914307.36086,-132410377066.51402,-161465549195.87524,-132961540542.96703,-67048825563.617485,27073048140.349026,24686252589.02754,15289524834.240807,HMDB0000158,C00082,L-Tyrosine,Amino acid metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>UDP,TRUE,0.223438842,0.819821729,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.223438842,0.819821729,-4770565.827,HMDB0000295,C00015,UDP,Pyrimidine metabolism,36395193.8,27551514.75,35801234.03,38604904.66,23658013.65,23173326.78,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>UDP-GlcNac,TRUE,-0.335146821,0.102193405,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.335146821,0.102193405,31530797.21,NA,NA,NA,Not assigned,119189221.1,116722886.7,125809878.7,176964503.3,140445867,138904007.8,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>UDP-hexose,TRUE,0.049293092,0.97872786,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.049293092,0.97872786,-2850405.04,NA,NA,NA,Not assigned,83177213.95,85226735.01,86170339.48,98757664.99,76499790.45,70765617.87,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>UMP,TRUE,0.731575405,0.021522042,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.731575405,0.021522042,-2109370.305,HMDB0000288,C00105,UMP,Pyrimidine metabolism,5604822.465,5083695.326,5221088.331,4136091.068,2724295.548,2721108.59,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>uric acid,TRUE,0.339082456,0.080469499,No Change,Not Significant,TRUE,-33.9269804260675,0.9997058672125008,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released/Consumed,None,None,0.339082456,0.080469499,-68512139.8,HMDB0000289,C00366,Urate,Purine metabolism,336995332.6,304106411.5,340184793.3,234697723.5,231711939.4,309340455,Not Significant,-33.9269804260675,0.9997058672125008,16331977410.204414,-16331977410.2044,Consumed,5.87701797485352e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-22789717996.85698,65960060380.90869,-103065983594.07104,12005878775.561075,-33770124616.563545,-16443417728.63839,43908796328.531906,2173013730.9821954,-29638392330.875477,HMDB0000289,C00366,Urate,Purine metabolism</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>uridine,TRUE,-0.061713367,0.998553608,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.061713367,0.998553608,34948.22481,HMDB0000296,C00299,Uridine,Pyrimidine metabolism,1082080.177,608915.2594,707946.6923,832756.5818,656573.2849,1014456.936,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>UTP,TRUE,0.217915892,0.949481404,No Change,Not Significant,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.217915892,0.949481404,-11304254.07,HMDB0000285,C00075,UTP,Pyrimidine metabolism,90710931.49,56997541.11,94191395.01,107080622.8,48853010.39,52053472.2,Not Significant,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Val-Lys,TRUE,-0.780101416,8.9125127043177e-5,No Change,Significant Negative,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,-0.780101416,8.9125127043177e-5,16771377.26,HMDB0029132,NA,NA,Amino acid metabolism,23639151.1,21748553.5,24760807.87,42890269.18,38442608.97,39129766.09,Significant Negative,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>valine,TRUE,-0.118224697,0.594813983,No Change,Not Significant,TRUE,-36.7246376672365,7.646776467584715e-8,DOWN,DOWN,TRUE,Intra Not Significant + core DOWN_Released/Consumed,core_DOWN (Released/Consumed),core_DOWN (Released/Consumed),-0.118224697,0.594813983,25708899.39,HMDB0000883,C00183,L-Valine,Valine, leucine and isoleucine biosynthesis,315279253.2,292344631.6,295515888,313973606.8,305676938.7,360615925.5,Not Significant,-36.7246376672365,7.646776467584715e-8,113557943172.13937,-113557943172.139,Consumed,2.93254852294922e-05,Released,Consumed in 786-M1A  and Released HK2,Released/Consumed,-118873714902.30124,-85575769918.18422,-130457945572.56377,-119265479139.48428,-113616806328.1631,-5101628034.348264,-14803865995.795729,35106820799.222305,-15201326769.078196,HMDB0000883,C00183,L-Valine,Valine, leucine and isoleucine biosynthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>valine-d8,TRUE,0.516596794,0.002673479,No Change,Significant Positive,FALSE,NA,NA,No Change,Not Detected,FALSE,Background = FALSE,Background = FALSE,Background = FALSE,0.516596794,0.002673479,-674237712.7,NA,NA,NA,NA,2390155102,2227283635,2102958682,1483137881,1600737730,1613808669,Significant Positive,NA,NA,NA,NA,NA,NA,NA,NA,Not Detected,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA,NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>xanthine,TRUE,-0.071824048,0.989393606,No Change,Not Significant,TRUE,33.2325604962577,0.07790793938422658,No Change,Not Significant,TRUE,Intra Not Significant + core Not Significant_Released/Consumed,None,None,-0.071824048,0.989393606,692460.9992,HMDB0000292,C00385,Xanthine,Purine metabolism,15393862.43,11632708.28,13670747.19,12150459.97,11849147.52,18775093.42,Not Significant,33.2325604962577,0.07790793938422658,-10092471741.82114,10092471741.8211,Released,-3.814697265625e-06,Consumed,Released in 786-M1A and Consumed HK2,Released/Consumed,4854974013.82883,10527089813.379648,16033206392.766642,9298552623.97913,9748535865.15136,5717176779.012968,4193567812.1094074,-16970282597.653488,7059538006.531097,HMDB0000292,C00385,Xanthine,Purine metabolism</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A46"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Regulation.Grouping.SiRCle.cluster.Name.Number.of.Features</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RG1_All,Background = FALSE,151</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra UP + core Not Significant_Released/Consumed,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra UP + core UP_Released/Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core Not Significant_Released/Consumed,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Negative + core DOWN_Released/Consumed,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra UP + core DOWN_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra DOWN + core DOWN_Released/Consumed,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core Not Significant_Released,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra DOWN + core UP_Released,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Positive + core DOWN_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Positive + core Not Significant_Consumed,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Negative + core DOWN_Consumed,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Positive + core UP_Released/Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core Significant Positive_Released,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra DOWN + core Not Significant_Released/Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core DOWN_Released/Consumed,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Positive + core Not Significant_Released/Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core UP_Released/Consumed,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra DOWN + core Not Significant_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Negative + core Not Significant_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Significant Negative + core Not Significant_Released/Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core UP_Released,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra UP + core Not Significant_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RG1_All,Intra Not Significant + core DOWN_Consumed,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Background = FALSE,151</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RG2_Significant,None,22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Both_UP (Released/Consumed),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Both_DOWN (Released/Consumed),10</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Opposite (Consumed DOWN),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Opposite (Released UP),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RG2_Significant,Both_DOWN (Consumed),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RG2_Significant,core_DOWN (Released/Consumed),4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>RG2_Significant,core_UP (Released/Consumed),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>RG2_Significant,core_UP (Released),1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>RG2_Significant,core_DOWN (Consumed),1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>RG3_Change,Background = FALSE,151</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RG3_Change,None,22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>RG3_Change,Both_UP (Released/Consumed),1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>RG3_Change,core_DOWN (Released/Consumed),7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>RG3_Change,Opposite (Consumed DOWN),1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RG3_Change,Both_DOWN (Released/Consumed),7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>RG3_Change,Opposite (Released UP),2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>RG3_Change,core_DOWN (Consumed),4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>RG3_Change,core_UP (Released/Consumed),3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>RG3_Change,core_UP (Released),1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T230"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
